--- a/responses/zero-shot/auswertung.xlsx
+++ b/responses/zero-shot/auswertung.xlsx
@@ -464,14 +464,16 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>| Direktes Zitat \( T_i \) | Bewertung \( f_i \) |
-|--------------------------|---------------------|
-| "Ausgestaltung:  Cognitive-Load-Theorie" | 1 |
-| "Cognitive Theorie of Multimedia Learning (CTML)" | 1 |
-| "ICAP-Modell" | 1 |
-| "Multimediaprinzip: Lernerfolg größer, wenn Bilder und Texte enthalten sind" | 1 |
-| "man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)" | 1 |
-| **Gesamtbewertung**      | 5                   |</t>
+          <t>```markdown
+| Direktes Zitat \( T_i \)                                                                  | Bewertung \( f_i \) |
+|------------------------------------------------------------------------------------------|---------------------|
+| "Ausgestaltung:  Cognitive-Load-Theorie"                                                 | 1                   |
+| "Cognitive Theorie of Multimedia Learning (CTML)"                                        | 1                   |
+| "ICAP-Modell"                                                                            | 1                   |
+| "Multimediale Inhalte müssen beide Informationsverarbeitungskanäle ansprechen"           | 1                   |
+| "Lerninhalte sollten nicht einfach nur präsentiert werden, sondern ... interaktive Aktivitäten schaffen" | 1                   |
+| **Gesamtbewertung**                                                                      | 5                   |
+```</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -486,14 +488,14 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>| Direktes Zitat \( T_i \)                                                                                     | Bewertung \( f_i \) |
-|--------------------------------------------------------------------------------------------------------------|---------------------|
-| "cognitive-load-theorie"                                                                                     | 1                   |
-| "Das ICAP-Modell von Chi &amp; Wylie"                                                                            | 1                   |
-| "Die Cognitive Theory of Multimedia Learning (CTML) von Mayer"                                               | 1                   |
-| "Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten"                                       | 1                   |
-| "daher würde ich alle Lernaktivitäten miteinander vereinen, um den bestmöglichen Vortrag zu haben"            | 1                   |
-| **Gesamtbewertung**                                                                                          | 5                   |</t>
+          <t>| Direktes Zitat \( T_i \)                                                                                                                                                                                                                                                                                  | Bewertung \( f_i \) |
+|-----------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------|---------------------|
+| "cognitive-load-theorie   = wie wir Lernmaterialien nutzen  wie Informationen aus dem Arbeitsgedächtnis verarbeitet werden, dies ist begrenzt ... daher weniger Text, da man sich vorgelesenen Text besser merken kann (siehe Cognitive Theory of Multimedia)"                                          | 1                   |
+| "Das ICAP-Modell von Chi &amp; Wylie  ... daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) ! ... Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können." | 1                   |
+| "Multimedia = bild + wörter meistens ... dann Integration mit Vorwissen -&gt; dann lernen ... daher beide Kanäle ansprechen ! ... multimediales lernen ist besser!"                                                                                                                                          | 1                   |
+| "Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten  Powerpointfolien im Vortrag - grafische Darstellung ... Infos räumlich nah und relativ nah im zeitlichen abstand"                                                                                                                   | 1                   |
+| "Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, auf welcher überwiegend Bilder zu sehen sind, welche ich gleichzeitig mit Worten erkläre ... daher würde ich alle Lernaktivitäten miteinander vereinen, um den bestmöglichen Vortrag zu haben."                | 1                   |
+| **Gesamtbewertung**                                                                                                                                                                                                                                                                                       | 5                   |</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">

--- a/responses/zero-shot/auswertung.xlsx
+++ b/responses/zero-shot/auswertung.xlsx
@@ -464,16 +464,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>```markdown
-| Direktes Zitat \( T_i \)                                                                  | Bewertung \( f_i \) |
-|------------------------------------------------------------------------------------------|---------------------|
-| "Ausgestaltung:  Cognitive-Load-Theorie"                                                 | 1                   |
-| "Cognitive Theorie of Multimedia Learning (CTML)"                                        | 1                   |
-| "ICAP-Modell"                                                                            | 1                   |
-| "Multimediale Inhalte müssen beide Informationsverarbeitungskanäle ansprechen"           | 1                   |
-| "Lerninhalte sollten nicht einfach nur präsentiert werden, sondern ... interaktive Aktivitäten schaffen" | 1                   |
-| **Gesamtbewertung**                                                                      | 5                   |
-```</t>
+          <t>| Direktes Zitat \( T_i \)                                                                                 | Bewertung \( f_i \) |
+|----------------------------------------------------------------------------------------------------------|---------------------|
+| "Ausgestaltung:  Cognitive-Load-Theorie"                                                                 | 1                   |
+| "Cognitive Theorie of Multimedia Learning (CTML)"                                                        | 1                   |
+| "ICAP-Modell"                                                                                            | 1                   |
+| "Lernen ist besser, wenn der Text dazu noch gesprochen wird und Hintergrundmusik sollte aus sein"       | 1                   |
+| "Prinzipien zur Gestaltung von multimedialen Inhalten"                                                   | 1                   |
+| **Gesamtbewertung**                                                                                      | 5                   |</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -488,14 +486,14 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>| Direktes Zitat \( T_i \)                                                                                                                                                                                                                                                                                  | Bewertung \( f_i \) |
-|-----------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------|---------------------|
-| "cognitive-load-theorie   = wie wir Lernmaterialien nutzen  wie Informationen aus dem Arbeitsgedächtnis verarbeitet werden, dies ist begrenzt ... daher weniger Text, da man sich vorgelesenen Text besser merken kann (siehe Cognitive Theory of Multimedia)"                                          | 1                   |
-| "Das ICAP-Modell von Chi &amp; Wylie  ... daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) ! ... Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können." | 1                   |
-| "Multimedia = bild + wörter meistens ... dann Integration mit Vorwissen -&gt; dann lernen ... daher beide Kanäle ansprechen ! ... multimediales lernen ist besser!"                                                                                                                                          | 1                   |
-| "Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten  Powerpointfolien im Vortrag - grafische Darstellung ... Infos räumlich nah und relativ nah im zeitlichen abstand"                                                                                                                   | 1                   |
-| "Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, auf welcher überwiegend Bilder zu sehen sind, welche ich gleichzeitig mit Worten erkläre ... daher würde ich alle Lernaktivitäten miteinander vereinen, um den bestmöglichen Vortrag zu haben."                | 1                   |
-| **Gesamtbewertung**                                                                                                                                                                                                                                                                                       | 5                   |</t>
+          <t>| Direktes Zitat \( T_i \)                                                                                           | Bewertung \( f_i \) |
+|---------------------------------------------------------------------------------------------------------------------|---------------------|
+| "cognitive-load-theorie   = wie wir Lernmaterialien nutzen"                                                         | 1                   |
+| "Das ICAP-Modell von Chi &amp; Wylie"                                                                                   | 1                   |
+| "Die Cognitive Theory of Multimedia Learning (CTML) von Mayer"                                                      | 1                   |
+| "Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten"                                              | 1                   |
+| "Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, [...] interaktiv sich austauschen" | 1                   |
+| **Gesamtbewertung**                                                                                                 | 5                   |</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">

--- a/responses/zero-shot/auswertung.xlsx
+++ b/responses/zero-shot/auswertung.xlsx
@@ -431,26 +431,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="1.8" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="8.1" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="8.1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>Textaufgabe</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Begruendung</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Punktzahl</t>
         </is>
@@ -459,45 +465,94 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>Ausgestaltung:  Cognitive-Load-Theorie  - Grundannahme 1: Arbeitsgedächtnis ist kapazitivbeschränkt  - Grundannahme 2: unterschiedliche Prozesse im Arbeitsgedächtnis während dem Lernen     - inhaltsbedingte kognitive Belastung     - sachfremde kognitive Belastung     - lernrelevante kognitive Belastung  - Grundannahme 3: kognitive Belastungen wirken additiv  - Ziel: sachfremde kognitive Belastung möglichst gering und lernrelevante Belastung möglichst hoch halten  - Vermeidung von Sachen, die nichts mit dem Thema zu tuen haben, also die Vermeidung von sachfremden kognitiven Belastungen (z.B. Hintergrundmusik, komplexe Darstellungen)    Cognitive Theorie of Multimedia Learning (CTML)  - Definition: Annahmen, welche Prozesse im Gedächtnis bei der Verarbeitung von multimedial präsentierten Informationen ablaufen  - Grundannahme 1: Lernen bedeutet aktive Informationsverarbeitung  - Grundannahme 2: Kapazität für Informationsverarbeitung ist massiv beschränkt  - Grundannahme 3: zwei Verarbeitungskanäle sind beteiligt      - visueller-piktorialer Kanal: Verarbeitung von Bildern     - auditorisch-verbaler Kanal: Verarbeitung von Texten  - Besteht aus Bilder und Wörter und gelangt in sensorisches Gedächtnis (Ohren und Augen)  - im Arbeitsgedächtnis: Aufmerksamkeitsprozesse (können nicht alle Informationen verarbeiten)  - Unterscheidung von verbalem und bildhaftem Modell im Arbeitsgedächtnis  - Multimediale Inhalte müssen beide Informationsverarbeitungskanäle ansprechen  - Gründe: effiziente Nutzung der limitierten Verarbeitungskapazität    ICAP-Modell  - Annahmen dazu, in welcher Beziehung äußerlich sichtbare Lernaktivitäten mit unsichtbaren kognitiven Lernprozessen stehen  - Unterscheidung:    - passiv: z.B. ein Erklärvideo ansehen    - aktiv: z.B. in einem Text wichtige Stellen unterstreichen    - konstruktiv: z.B. eine Mindmap erstellen    - interaktiv: z.B. mit Kommilitonen über Lerninhalte diskutieren  - Zentrale Annahme: Wichtigkeit nach folgender Reihenfolge I &gt; C &gt; A &gt; P  - reines Ansehen und Zuhören weniger hilfreich  - Lernenden müssen sich kognitiv intensiv mit Lerninhalten beschäftigen    Studie zur Cognitiv-Load- Theorie  - Studie zum Blutkreisllauf anhand von drei Webseiten  - unterschiedliche Webseiten (Bilder und Text mit Musik, Bilder und Text ohne Musik, Bilder und gesprochener Text mit Musik)  - Wissenserwerb bei visueller Information mit Audioinformation ist am Höchsten  - Reaktionszeiten hat wenig Effekt ohne Audioinformation  - Audiovisuelle präsentierte Informationen werden besser behalten als nur visuell präsentierte Informationen  - Hintergrundmusik erhöht Reaktionszeit  - Lernen ist besser, wenn der Text dazu noch gesprochen wird und Hintergrundmusik sollte aus sein    Studie zu Cognitive Theorie of Multimedia Learning  - Vesuchsaufbau: Materialien wie Blitze entstehen (Videos)  - zwei Versuchsbedingungen    - Text zu Video wurde geschrieben    - Text zu Video wurde gesprochen  - Erinnerungstest nach bestimmter Zeit   - Ergebnis: Teilnehmer, die das Video mit gesprochenem Text gesehen haben, haben besser abgeschnitten  - Animation in Kombination mit eingeblendetem Text überfordert  - Ziel: Lerninhalte sollten sowohl auditive als auch visuelle Kanäle nutzen    Studie zu ICAP-Modell  - Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest  - Zufällige Zuweisung:     - Passiv: Text laut lesen    - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen    - konstruktiv: graphische Darstellung selbstständig vervollständigen    - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen  - Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab   - ICAP- Hypothese wurde bestätigt wie im ICAP-Modell beschrieben  - Lerninhalte sollten nicht einfach nur präsentiert werden, sondern man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)    Prinzipien zur Gestaltung von multimedialen Inhalten  - Multimediaprinzip: Lernerfolg größer, wenn Bilder und Texte enthalten sind  - Modalitätsprinzip: Lerninhalte mit Bildern und Texten ( Lernerfolg besser, wenn Text gesprochen wird)  - Redundanzprinzip: Lerninhalte mit Bildern und Texten sollten nicht wiederholt , sondern ergänzt werden  - Räumliches Kontiguitätsprinzip: Räumlicher Abstand sollte nicht zu groß sein zwischen Bildern/Grafiken und dazugehörigen Texten  - zeitliches Kontiguitätsprinzip: Lerninhalte mit gesprochenem Text und Bildern sollten möglichst gleichzeitig passieren  - Kohärenzprinzip: Multimediale Darstellungen sollten sich auf die Präsentation wesentlicher Informationen beschränken  - Segmentierungsprinzip: bei komplexen Lerninhalten nicht alles auf einmal präsentieren, sondern schrittweise  - Signalisierungsprinzip: durch sprachliche oder visuelle Merker Wichtiges markieren  - Selbsterklärungsprinzip: Lernende verstehen Lerninhalte besser, wenn sie es sich immmer wieder selbst erklären</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>| Direktes Zitat \( T_i \)                                                                                 | Bewertung \( f_i \) |
-|----------------------------------------------------------------------------------------------------------|---------------------|
-| "Ausgestaltung:  Cognitive-Load-Theorie"                                                                 | 1                   |
-| "Cognitive Theorie of Multimedia Learning (CTML)"                                                        | 1                   |
-| "ICAP-Modell"                                                                                            | 1                   |
-| "Lernen ist besser, wenn der Text dazu noch gesprochen wird und Hintergrundmusik sollte aus sein"       | 1                   |
-| "Prinzipien zur Gestaltung von multimedialen Inhalten"                                                   | 1                   |
-| **Gesamtbewertung**                                                                                      | 5                   |</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>5</v>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>begruendung_lernaktivitaet
++1 Punkt: Erklärung des ICAP-Modells
+→ „Annahmen dazu, in welcher Beziehung äußerlich sichtbare Lernaktivitäten mit unsichtbaren kognitiven Lernprozessen stehen“
++1 Punkt: Erklärung der Aktivitätsstufen des Akronyms "ICAP"
+→ „Unterscheidung: - passiv: z.B. ein Erklärvideo ansehen - aktiv: z.B. in einem Text wichtige Stellen unterstreichen - konstruktiv: z.B. eine Mindmap erstellen - interaktiv: z.B. mit Kommilitonen über Lerninhalte diskutieren“
++1 Punkt: Nennung der Aktivitätsstufe, die verwendet wird
+→ „z.B. mit Kommilitonen über Lerninhalte diskutieren“
++1 Punkt: Begründung, weshalb diese Aktivitätsstufe gewählt wird
+→ „Wichtigkeit nach folgender Reihenfolge I &gt; C &gt; A &gt; P – reines Ansehen und Zuhören weniger hilfreich – Lernenden müssen sich kognitiv intensiv mit Lerninhalten beschäftigen“
++2 Punkte: Begründung mittels Studie zu ICAP (Menekse et al., 2013)
+→ „Studie zu ICAP-Modell - Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest – Zufällige Zuweisung: - Passiv: Text laut lesen - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen - konstruktiv: graphische Darstellung selbstständig vervollständigen - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen - Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab - ICAP- Hypothese wurde bestätigt wie im ICAP-Modell beschrieben – Lerninhalte sollten nicht einfach nur präsentiert werden, sondern man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)“
++1 Punkt: Nennung der Teilnehmeranzahl (TN): 120 TNs
+→ „120 TNs“
++1 Punkt: Versuchsaufbau/ Versuchsbedingungen: Vier Gruppen zum Thema Chemie mit vier Bedingungen
+→ „Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest – Zufällige Zuweisung: - Passiv: Text laut lesen - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen - konstruktiv: graphische Darstellung selbstständig vervollständigen - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen“
++1 Punkt: Ergebnisse: Bestätigung der ICAP-Hypothese, dass Interaktive Lernaktivitäten das höchste Potenzial haben, gefolgt von konstruktiven, gefolgt von aktiven und gefolgt von passiven
+→ „Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab - ICAP- Hypothese wurde bestätigt wie im ICAP-Modell beschrieben“
++1 Punkt: 1. Implikation: Lerninhalte sollten nicht einfach nur präsentiert werden
+→ „Lerninhalte sollten nicht einfach nur präsentiert werden“
++1 Punkt: 2. Implikation: Lehrperson sollte Gelegenheiten für interaktive Aktivitäten schaffen
+→ „man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)“
++1 Punkt: Interaktive Lernaktivitäten: Vervollständigung einer graphischen Darstellung in Zweiergruppen/ mit anderen diskutieren
+→ „graphische Darstellung in Zweiergruppen vervollständigen“
++1 Punkt: konstruktive Lernaktivitäten: Graphische Darstellung selbstständig und allein vervollständigen/ eine Mindmap erstellen
+→ „graphische Darstellung selbstständig vervollständigen“
++1 Punkt: aktive Lernaktivitäten: Informationstext laut vorlesen und wichtigste Inhalte unterstreichen/
+→ „Text laut lesen und wichtigste Inhalte unterstreichen“
++1 Punkt: passive Lernaktivitäten: Informationstext laut vorlesen/ Erklärvideo ansehen
+→ „Text laut lesen“
+Gesamtpunktzahl: 15</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>AG0EVJU2003FU  Notizen:     cognitive-load-theorie   = wie wir Lernmaterialien nutzen  wie Informationen aus dem Arbeitsgedächtnis verarbeitet werden, dies ist begrenzt  ungünstig: Hintergrundmusik, die nichts mit dem Lernenden zu tun hat  günstig: was man aufwendet, um neue Schemata zu lernen  Personen mit hoher inhaltsbedingte Belastung - ebenso hohe sachfremde B. - ist lernen kaum möglich   Personen mit niedriger inhaltsbedingte Belastung aufgrund von Vorwissen - ebenso niedrige sachfremde B. - Potenzial zum lernen lernen möglich   man soll darauf achten, dass sachfremde Belastung gering ist und keine Ablenkung von Hintergrundmusik      Eine exemplarische empirische Studie zur Cognitive-Load-Theory  2004 10 Hochschulstudenten erhielten Informationssystem zum Thema   Blutkreislauf   3 Webseiten:  1. visuelle Bilder + Text + ohne Hintergrundmusik  2. visuelle Bilder + Text + Hintergrundmusik  3. visuelle Bilder + Text vorgelesen + Hintergrundmusik    Wie lernen sie/ was nehmen sie mit? Wie ist Reaktionszeit auf Ton?   man lernt anscheinend mehr, wenn Bilder mit Ton vorhanden ist   bei nur visueller Informationen Hintergrundmusik relativ egal, bei zusätzlichen audio Informativen eher keine Hintergrundmusik    Das ICAP-Modell von Chi &amp; Wylie  passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen   körperlich aktive = wichtige Infos unterstreichen   konstruktiv = Mindmap erstellen  interaktiv = mit anderen austauschen -  am besten - neues wissen produzieren - tiefes Verständnis   also reines zuhören nicht so gut !  aber nur wenn Auseinandersetzung auch über das Lernende ist    Eine exemplarische empirische Studie zum ICAP-Modell  120 Studierende  zum Thema Chemie   Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest   interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten  daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !     Die Cognitive Theory of Multimedia Learning (CTML) von Mayer  welche Prozesse laufen ab, wenn wir Multimedia benutzen   Multimedia = bild + wörter meistens -&gt; sensorisches Gedächtnis -&gt; Arbeitsgedächtnis: alle Infos können wir nicht gleichzeitig aufnehmen  dann Integration mit Vorwissen -&gt; dann lernen     daher beide Kanäle ansprechen !  Überlastung eines der beiden Kanäle sollte vermieden werden!    Eine exemplarische empirische Studie zur Cognitive Theory of Multimedia Learning (CTML)  1: Bilder + geschriebener Text  2. Bilder + vorgelesener Text  danach Erinnerungstest   bildlicher Inhalt muss mit auditiven Inhalt passend sein! multimediales lernen ist besser!    Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten  Powerpointfolien im Vortrag - grafische Darstellung  Videos mit Text  Infos räumlich nah und relativ nah im zeitlichen abstand   Comic in einer ecke nicht gut, da so Aufmerksamkeit abgelenkt wird    Aufgabenstellung:     Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, auf welcher überwiegend Bilder zu sehen sind, welche ich gleichzeitig mit Worten erkläre. So wird die audio und visuelle Belastung angesprochen. Daher weniger Text, da man sich vorgelesenen Text besser merken kann (siehe Cognitive Theory of Multimedia). Zusätzlich würde ich anfangs auf Themen aus dem Unterricht oder ganz allgemeine Themen ansprechen, so dass jeder bei dem gleichen Wissenstand abgeholt werden kann bei gleicher inhaltsbedingter Belastung (siehe Cognitive-Load-Theory). Außerdem würde ich auch ein Video zeigen, welches das Gezeigte und Gesprochene noch einmal mit Hintergrundmusik wiederholt. Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.   daher würde ich alle Lernaktivitäten miteinander vereinen, um den bestmöglichen Vortrag zu haben.</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>| Direktes Zitat \( T_i \)                                                                                           | Bewertung \( f_i \) |
-|---------------------------------------------------------------------------------------------------------------------|---------------------|
-| "cognitive-load-theorie   = wie wir Lernmaterialien nutzen"                                                         | 1                   |
-| "Das ICAP-Modell von Chi &amp; Wylie"                                                                                   | 1                   |
-| "Die Cognitive Theory of Multimedia Learning (CTML) von Mayer"                                                      | 1                   |
-| "Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten"                                              | 1                   |
-| "Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, [...] interaktiv sich austauschen" | 1                   |
-| **Gesamtbewertung**                                                                                                 | 5                   |</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>## Kategorie
+begruendung_lernaktivitaet
++1 Punkt: Erklärung des ICAP-Modells
+→ „Das ICAP-Modell von Chi &amp; Wylie passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen körperlich aktive = wichtige Infos unterstreichen konstruktiv = Mindmap erstellen interaktiv = mit anderen austauschen - am besten - neues wissen produzieren - tiefes Verständnis also reines zuhören nicht so gut ! aber nur wenn Auseinandersetzung auch über das Lernende ist“
++1 Punkt: Erklärung der Aktivitätsstufen des Akronyms „ICAP“
+→ „passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen körperlich aktive = wichtige Infos unterstreichen konstruktiv = Mindmap erstellen interaktiv = mit anderen austauschen - am besten - neues wissen produzieren - tiefes Verständnis“
++1 Punkt: Nennung der Aktivitätsstufe, die verwendet wird
+→ „Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.“
++1 Punkt: Begründung, weshalb diese Aktivitätsstufe gewählt wird
+→ „daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !“
++2 Punkte: Begründung mittels Studie zu ICAP (Menekse et al., 2013)
+→ „Eine exemplarische empirische Studie zum ICAP-Modell 120 Studierende zum Thema Chemie Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten“
++1 Punkt: Nennung der Teilnehmeranzahl (TN): 120 TNs
+→ „Eine exemplarische empirische Studie zum ICAP-Modell 120 Studierende zum Thema Chemie“
++1 Punkt: Versuchsaufbau/Versuchsbedingungen: Vier Gruppen zum Thema Chemie mit vier Bedingungen
+→ „Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest“
++1 Punkt: Ergebnisse: Bestätigung der ICAP-Hypothese, dass Interaktive Lernaktivitäten das höchste Potenzial haben, gefolgt von konstruktiven, gefolgt von aktiven und gefolgt von passiven
+→ „interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten“
++1 Punkt: 1. Implikation: Lerninhalte sollten nicht einfach nur präsentiert werden
+→ „daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !“ 
++1 Punkt: 2. Implikation: Lehrperson sollte Gelegenheiten für interaktive Aktivitäten schaffen
+→ „Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.“
++1 Punkt: Interaktive Lernaktivitäten: Vervollständigung einer graphischen Darstellung in Zweiergruppen/mit anderen diskutieren
+→  Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.
+Gesamtpunktzahl: 12</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/responses/zero-shot/auswertung.xlsx
+++ b/responses/zero-shot/auswertung.xlsx
@@ -1,37 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vincent Dusanek\Documents\GitHub\ai-rater-prompts\responses\zero-shot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7282B066-8EC7-4535-9E7F-4B02A01C7B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Textaufgabe</t>
+  </si>
+  <si>
+    <t>Begruendung</t>
+  </si>
+  <si>
+    <t>Punktzahl</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Ausgestaltung:  Cognitive-Load-Theorie  - Grundannahme 1: Arbeitsgedächtnis ist kapazitivbeschränkt  - Grundannahme 2: unterschiedliche Prozesse im Arbeitsgedächtnis während dem Lernen     - inhaltsbedingte kognitive Belastung     - sachfremde kognitive Belastung     - lernrelevante kognitive Belastung  - Grundannahme 3: kognitive Belastungen wirken additiv  - Ziel: sachfremde kognitive Belastung möglichst gering und lernrelevante Belastung möglichst hoch halten  - Vermeidung von Sachen, die nichts mit dem Thema zu tuen haben, also die Vermeidung von sachfremden kognitiven Belastungen (z.B. Hintergrundmusik, komplexe Darstellungen)    Cognitive Theorie of Multimedia Learning (CTML)  - Definition: Annahmen, welche Prozesse im Gedächtnis bei der Verarbeitung von multimedial präsentierten Informationen ablaufen  - Grundannahme 1: Lernen bedeutet aktive Informationsverarbeitung  - Grundannahme 2: Kapazität für Informationsverarbeitung ist massiv beschränkt  - Grundannahme 3: zwei Verarbeitungskanäle sind beteiligt      - visueller-piktorialer Kanal: Verarbeitung von Bildern     - auditorisch-verbaler Kanal: Verarbeitung von Texten  - Besteht aus Bilder und Wörter und gelangt in sensorisches Gedächtnis (Ohren und Augen)  - im Arbeitsgedächtnis: Aufmerksamkeitsprozesse (können nicht alle Informationen verarbeiten)  - Unterscheidung von verbalem und bildhaftem Modell im Arbeitsgedächtnis  - Multimediale Inhalte müssen beide Informationsverarbeitungskanäle ansprechen  - Gründe: effiziente Nutzung der limitierten Verarbeitungskapazität    ICAP-Modell  - Annahmen dazu, in welcher Beziehung äußerlich sichtbare Lernaktivitäten mit unsichtbaren kognitiven Lernprozessen stehen  - Unterscheidung:    - passiv: z.B. ein Erklärvideo ansehen    - aktiv: z.B. in einem Text wichtige Stellen unterstreichen    - konstruktiv: z.B. eine Mindmap erstellen    - interaktiv: z.B. mit Kommilitonen über Lerninhalte diskutieren  - Zentrale Annahme: Wichtigkeit nach folgender Reihenfolge I &gt; C &gt; A &gt; P  - reines Ansehen und Zuhören weniger hilfreich  - Lernenden müssen sich kognitiv intensiv mit Lerninhalten beschäftigen    Studie zur Cognitiv-Load- Theorie  - Studie zum Blutkreisllauf anhand von drei Webseiten  - unterschiedliche Webseiten (Bilder und Text mit Musik, Bilder und Text ohne Musik, Bilder und gesprochener Text mit Musik)  - Wissenserwerb bei visueller Information mit Audioinformation ist am Höchsten  - Reaktionszeiten hat wenig Effekt ohne Audioinformation  - Audiovisuelle präsentierte Informationen werden besser behalten als nur visuell präsentierte Informationen  - Hintergrundmusik erhöht Reaktionszeit  - Lernen ist besser, wenn der Text dazu noch gesprochen wird und Hintergrundmusik sollte aus sein    Studie zu Cognitive Theorie of Multimedia Learning  - Vesuchsaufbau: Materialien wie Blitze entstehen (Videos)  - zwei Versuchsbedingungen    - Text zu Video wurde geschrieben    - Text zu Video wurde gesprochen  - Erinnerungstest nach bestimmter Zeit   - Ergebnis: Teilnehmer, die das Video mit gesprochenem Text gesehen haben, haben besser abgeschnitten  - Animation in Kombination mit eingeblendetem Text überfordert  - Ziel: Lerninhalte sollten sowohl auditive als auch visuelle Kanäle nutzen    Studie zu ICAP-Modell  - Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest  - Zufällige Zuweisung:     - Passiv: Text laut lesen    - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen    - konstruktiv: graphische Darstellung selbstständig vervollständigen    - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen  - Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab   - ICAP- Hypothese wurde bestätigt wie im ICAP-Modell beschrieben  - Lerninhalte sollten nicht einfach nur präsentiert werden, sondern man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)    Prinzipien zur Gestaltung von multimedialen Inhalten  - Multimediaprinzip: Lernerfolg größer, wenn Bilder und Texte enthalten sind  - Modalitätsprinzip: Lerninhalte mit Bildern und Texten ( Lernerfolg besser, wenn Text gesprochen wird)  - Redundanzprinzip: Lerninhalte mit Bildern und Texten sollten nicht wiederholt , sondern ergänzt werden  - Räumliches Kontiguitätsprinzip: Räumlicher Abstand sollte nicht zu groß sein zwischen Bildern/Grafiken und dazugehörigen Texten  - zeitliches Kontiguitätsprinzip: Lerninhalte mit gesprochenem Text und Bildern sollten möglichst gleichzeitig passieren  - Kohärenzprinzip: Multimediale Darstellungen sollten sich auf die Präsentation wesentlicher Informationen beschränken  - Segmentierungsprinzip: bei komplexen Lerninhalten nicht alles auf einmal präsentieren, sondern schrittweise  - Signalisierungsprinzip: durch sprachliche oder visuelle Merker Wichtiges markieren  - Selbsterklärungsprinzip: Lernende verstehen Lerninhalte besser, wenn sie es sich immmer wieder selbst erklären</t>
+  </si>
+  <si>
+    <t>### ICAP-Modell Bezug (max. 4 Punkte)
++1 Punkt: Erklärung des ICAP-Modells  
+→ „ICAP-Modell - Annahmen dazu, in welcher Beziehung äußerlich sichtbare Lernaktivitäten mit unsichtbaren kognitiven Lernprozessen stehen.“
++1 Punkt: Erklärung der Aktivitätsstufen des Akronyms ICAP  
+→ „Unterscheidung: - passiv: z.B. ein Erklärvideo ansehen - aktiv: z.B. in einem Text wichtige Stellen unterstreichen - konstruktiv: z.B. eine Mindmap erstellen - interaktiv: z.B. mit Kommilitonen über Lerninhalte diskutieren.“
++1 Punkt: Nennung der verwendeten Aktivitätsstufe  
+→ „Zufällige Zuweisung: - Passiv: Text laut lesen - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen - konstruktiv: graphische Darstellung selbstständig vervollständigen - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen.“
++1 Punkt: Begründung, weshalb diese Stufe gewählt wird  
+→ „Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab.“
+Zwischensumme: 4 Punkte  
+---
+### Empirischer Bezug zur ICAP-Studie (max. 7 Punkte)
++2 Punkte: Begründung mittels Studie zu ICAP (Menekse et al., 2013)  
+→ „Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest.“
++1 Punkt: Nennung der Teilnehmeranzahl  
+→ „Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab.“
++1 Punkt: Beschreibung des Versuchsdesigns  
+→ „Zufällige Zuweisung: - Passiv: Text laut lesen - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen - konstruktiv: graphische Darstellung selbstständig vervollständigen - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen.“
++1 Punkt: Ergebnisse korrekt beschrieben  
+→ „Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab.“
++1 Punkt: Implikation 1 – Inhalte nicht nur präsentieren  
+→ „Lerninhalte sollten nicht einfach nur präsentiert werden.“
++1 Punkt: Implikation 2 – Interaktive Lerngelegenheiten schaffen  
+→ „...man sollte Gelegenheiten für interaktive Aktivitäten schaffen (Gruppenarbeiten).“
+Zwischensumme: 7 Punkte  
+---
+### Beispiele der Aktivitätsstufen (max. 4 Punkte)
++1 Punkt: Interaktive Lernaktivitäten  
+→ „interaktiv: graphische Darstellung in Zweiergruppen vervollständigen.“
++1 Punkt: Konstruktive Lernaktivitäten  
+→ „konstruktiv: graphische Darstellung selbstständig vervollständigen.“
++1 Punkt: Aktive Lernaktivitäten  
+→ „aktiv: Text laut lesen und wichtigste Inhalte unterstreichen.“
++1 Punkt: Passive Lernaktivitäten  
+→ „passiv: Text laut lesen.“
+Zwischensumme: 4 Punkte  
+---
+### Gesamtpunktzahl  
+**15 Punkte**</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>A1annju2002st</t>
+  </si>
+  <si>
+    <t>Bitte teile den zu analysierenden Text mit, damit ich die systematische Textanalyse entsprechend dem Bewertungsschema durchführen kann.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>AG0EVJU2003FU  Notizen:     cognitive-load-theorie   = wie wir Lernmaterialien nutzen  wie Informationen aus dem Arbeitsgedächtnis verarbeitet werden, dies ist begrenzt  ungünstig: Hintergrundmusik, die nichts mit dem Lernenden zu tun hat  günstig: was man aufwendet, um neue Schemata zu lernen  Personen mit hoher inhaltsbedingte Belastung - ebenso hohe sachfremde B. - ist lernen kaum möglich   Personen mit niedriger inhaltsbedingte Belastung aufgrund von Vorwissen - ebenso niedrige sachfremde B. - Potenzial zum lernen lernen möglich   man soll darauf achten, dass sachfremde Belastung gering ist und keine Ablenkung von Hintergrundmusik      Eine exemplarische empirische Studie zur Cognitive-Load-Theory  2004 10 Hochschulstudenten erhielten Informationssystem zum Thema   Blutkreislauf   3 Webseiten:  1. visuelle Bilder + Text + ohne Hintergrundmusik  2. visuelle Bilder + Text + Hintergrundmusik  3. visuelle Bilder + Text vorgelesen + Hintergrundmusik    Wie lernen sie/ was nehmen sie mit? Wie ist Reaktionszeit auf Ton?   man lernt anscheinend mehr, wenn Bilder mit Ton vorhanden ist   bei nur visueller Informationen Hintergrundmusik relativ egal, bei zusätzlichen audio Informativen eher keine Hintergrundmusik    Das ICAP-Modell von Chi &amp; Wylie  passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen   körperlich aktive = wichtige Infos unterstreichen   konstruktiv = Mindmap erstellen  interaktiv = mit anderen austauschen -  am besten - neues wissen produzieren - tiefes Verständnis   also reines zuhören nicht so gut !  aber nur wenn Auseinandersetzung auch über das Lernende ist    Eine exemplarische empirische Studie zum ICAP-Modell  120 Studierende  zum Thema Chemie   Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest   interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten  daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !     Die Cognitive Theory of Multimedia Learning (CTML) von Mayer  welche Prozesse laufen ab, wenn wir Multimedia benutzen   Multimedia = bild + wörter meistens -&gt; sensorisches Gedächtnis -&gt; Arbeitsgedächtnis: alle Infos können wir nicht gleichzeitig aufnehmen  dann Integration mit Vorwissen -&gt; dann lernen     daher beide Kanäle ansprechen !  Überlastung eines der beiden Kanäle sollte vermieden werden!    Eine exemplarische empirische Studie zur Cognitive Theory of Multimedia Learning (CTML)  1: Bilder + geschriebener Text  2. Bilder + vorgelesener Text  danach Erinnerungstest   bildlicher Inhalt muss mit auditiven Inhalt passend sein! multimediales lernen ist besser!    Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten  Powerpointfolien im Vortrag - grafische Darstellung  Videos mit Text  Infos räumlich nah und relativ nah im zeitlichen abstand   Comic in einer ecke nicht gut, da so Aufmerksamkeit abgelenkt wird    Aufgabenstellung:     Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, auf welcher überwiegend Bilder zu sehen sind, welche ich gleichzeitig mit Worten erkläre. So wird die audio und visuelle Belastung angesprochen. Daher weniger Text, da man sich vorgelesenen Text besser merken kann (siehe Cognitive Theory of Multimedia). Zusätzlich würde ich anfangs auf Themen aus dem Unterricht oder ganz allgemeine Themen ansprechen, so dass jeder bei dem gleichen Wissenstand abgeholt werden kann bei gleicher inhaltsbedingter Belastung (siehe Cognitive-Load-Theory). Außerdem würde ich auch ein Video zeigen, welches das Gezeigte und Gesprochene noch einmal mit Hintergrundmusik wiederholt. Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.   daher würde ich alle Lernaktivitäten miteinander vereinen, um den bestmöglichen Vortrag zu haben.</t>
+  </si>
+  <si>
+    <t>### Codekategorie: ICAP-Modell Bezug (max. 4 Punkte)
++1 Punkt: Erklärung des ICAP-Modells  
+→ „Das ICAP-Modell von Chi &amp; Wylie formuliert Annahmen, in welcher Beziehung äußerlich sichtbare Lernaktivitäten mit unsichtbaren kognitiven (Lern-)Prozessen stehen.“
++1 Punkt: Erklärung der Aktivitätsstufen (ICAP)  
+→ „Passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues Wissen entsteht, aber nicht verknüpft mit aktuellem Wissen. Körperlich Aktive = Wichtige Infos unterstreichen. Konstruktiv = Mindmap erstellen. Interaktiv = Mit anderen austauschen - am besten - neues Wissen produzieren - tiefes Verständnis.“
++1 Punkt: Nennung der verwendeten Aktivitätsstufe  
+→ „Zuletzt würde ich nach dem IPAC-Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.“
++1 Punkt: Begründung, weshalb diese Stufe gewählt wird  
+→ „Interaktiv = Mit anderen austauschen - am besten - neues Wissen produzieren - tiefes Verständnis.“
+**Zwischensumme: 4 Punkte**
+---
+### Codekategorie: Empirischer Bezug zum ICAP-Modell (max. 7 Punkte)
++2 Punkte: Begründung mittels Studie zu ICAP (Menekse et al., 2013)  
+→ „Eine exemplarische empirische Studie zum ICAP-Modell: 120 Studierende zum Thema Chemie. Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest - Interaktive Aktivitäten am besten im Nachtest, passiv am schlechtesten.“
++1 Punkt: Nennung der Teilnehmeranzahl  
+→ „Eine exemplarische empirische Studie zum ICAP-Modell: 120 Studierende zum Thema Chemie.“
++1 Punkt: Beschreibung des Versuchsdesigns  
+→ „Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest.“
++1 Punkt: Ergebnisse  
+→ „Interaktive Aktivitäten am besten im Nachtest, passiv am schlechtesten.“
++1 Punkt: Implikation 1 – Inhalte nicht nur präsentieren  
+→ „Daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !“
++1 Punkt: Implikation 2 – Lehrperson soll interaktive Aktivitäten schaffen  
+→ „Daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !“
+**Zwischensumme: 7 Punkte**
+---
+### Codekategorie: Beispiele der Aktivitätsstufen (max. 4 Punkte)
++1 Punkt: Interaktive Lernaktivitäten  
+→ „Zuletzt würde ich nach dem IPAC-Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.“
++1 Punkt: Konstruktive Lernaktivitäten  
+→ „Konstruktiv = Mindmap erstellen.“
++1 Punkt: Aktive Lernaktivitäten  
+→ „Körperlich Aktive = Wichtige Infos unterstreichen.“
++1 Punkt: Passive Lernaktivitäten  
+→ „Passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues Wissen entsteht, aber nicht verknüpft mit aktuellem Wissen.“
+**Zwischensumme: 4 Punkte**
+---
+### Gesamtpunktzahl: 4 + 7 + 4 = **15 Punkte**</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>AL0FRAP2004GR  Arbeitsgedächtnis kann nicht beliebig viele Informationen verarbeiten (7+/-2) -&gt; man sollte sich auf den Folien auf wichtigste Informationen beschränken; Folien nicht zu überfüllt gestalten, da man sich in erster Linie auf die Erklärungen des Vortragenden konzentrieren soll (Folien dienen der Unterstützung); Vorwissen berücksichtigen (Person mit geringem Vorwissen kann mit einem bestimmten Thema nicht so viel anfangen, wie eine Person mit viel Vorwissen -&gt; muss sich erst einmal mit der Materie auseinandersetzen -&gt; deswegen müssen Folien so gestaltet sein, dass sie dem Vorwissen der Adressaten gerecht werden (nicht zu komplex); zudem sollten sich auf den Folien keine unnötigen Bilder befinden (sachfremde kognitive Belastung gering halten) -&gt; Kohärenzprinzip =&gt; beinhaltet in Cognitive-Load-Theorie;   exemplarische empirische Studie zur Cognitive-Load-Theorie: wie in dieser Studie beschrieben wird, werden audiovisuell präsentierte Informationen besser behalten als die, die nur visuell präsentiert werden -&gt; Folien sollten nicht mit Text überfüllt sein, sondern lieber themenbezogene Bilder und wichtige Stichpunkte, die dann vom Vortragenden erläutert werden -&gt;Modalitätsprinzip  Cognitive Theory of Multimedia Learning: Lernen bedeutet aktive Informationsverarbeitung -&gt; Folien sollten nicht nur statisch gestaltet werden, sondern die Zuhörer auch mit einbeziehen -&gt; Interaktivitätsprinzip (gelernter Stoff soll in Kleingruppen nachbesprochen werden -&gt; hoher Lernerfolg); im Arbeitsgedächtnis müssen die aufgenommenen Informationen, die durch das Auge und das Ohr aufgenommen werden, selektiert werden -&gt; auf den Folien sollten beide Informationskanäle angesprochen werden, da ein tieferes Verständnis des Stoffes erreicht werden kann, aber eine Überlastung soll vermieden werden (nicht visuelle Informationen und geschriebenen Text kombinieren, sondern Bilder mit gesprochenem Text) -&gt; Multimediaprinzip (Präsentation des Inhalts in textueller und bildhafter Form, wobei sich der Inhalt aber nicht wiederholen darf, sondern sich ergänzen -&gt; Redundanzprinzip)  diese Aussagen belegt auch die exemplarische empirische Studie zur Cognitive Theory of Multimedia Learning; es kommt zu einer besseren Verteilung, wenn beide Kanäle angesprochen werden und die gelernten Inhalte können besser mit dem Vorwissen verknüpft werden  sinnvolle Lernaktivitäten: Interaktiv ist sinnvoll, da man sich hierbei vertieft mit dem Stoff auseinandersetzt, indem man in einer Diskussion Gründe für seine eigene Position äußert. Gleichzeitig wird man aber auch mit anderen Meinungen konfrontiert wird, denen man sich nicht entziehen, da sonst keine Diskussion zustande kommt. Hierbei lernt man verschiedene Sichtweisen zu einem Thema kennen. Zudem wird automatisch die eigene Position hinterfragt und eventuell auch korrigiert. Ein weiterer wichtiger Punkt ist, dass in einer Diskussion auch das Vorwissen angeregt wird, was wiederum zu einer stärkeren Verknüpfung der gelernten Inhalte führt, die länger im Gedächtnis präsent sind (Tiefenverständnis -&gt; in einer gelungenen Diskussion werden kognitive Prozesse anregt).</t>
+  </si>
+  <si>
+    <t>### ICAP-Modell Bezug (max. 4 Punkte)
++0 Punkte: Erklärung des ICAP-Modells  
+→ Keine theoretische Definition des ICAP-Modells, die es als Verbindung zwischen äußerlich sichtbaren Lernaktivitäten und kognitiven Prozessen beschreibt.
++0 Punkte: Erklärung der Aktivitätsstufen (ICAP)  
+→ Keine explizite Nennung der vier Aktivitätsstufen "passiv, aktiv, konstruktiv, interaktiv".
++1 Punkt: Nennung der verwendeten Aktivitätsstufe  
+→ „Sinnvolle Lernaktivitäten: Interaktiv ist sinnvoll, da man sich hierbei vertieft mit dem Stoff auseinandersetzt, indem man in einer Diskussion Gründe für seine eigene Position äußert.“
++1 Punkt: Begründung, weshalb diese Stufe gewählt wird  
+→ „Hierbei lernt man verschiedene Sichtweisen zu einem Thema kennen. Zudem wird automatisch die eigene Position hinterfragt und eventuell auch korrigiert.“
+Zwischensumme: 2 Punkte  
+---
+### Empirischer Bezug zum ICAP-Modell (max. 7 Punkte)
++0 Punkte: Begründung mittels Studie zu ICAP (Menekse et al., 2013)  
+→ Keine Erwähnung der Studie von Menekse et al. (2013).
++0 Punkte: Nennung der Teilnehmeranzahl  
+→ Keine Angaben zur Teilnehmeranzahl einer relevanten Studie.
++0 Punkte: Beschreibung des Versuchsdesigns  
+→ Kein Nachweis eines Versuchsdesigns zur ICAP-Studie.
++0 Punkte: Ergebnisse der Studie zum ICAP-Modell  
+→ Ergebnisse der ICAP-Studie werden nicht behandelt.
++0 Punkte: Implikation 1 – Lerninhalte sollten nicht nur präsentiert werden  
+→ Keine explizite Erwähnung dazu im Kontext des ICAP-Modells.
++0 Punkte: Implikation 2 – Lehrperson sollte interaktive Aktivitäten schaffen  
+→ Keine Implikation, die eine Förderung interaktiver Aktivitäten im Zusammenhang mit ICAP fordert.
+Zwischensumme: 0 Punkte  
+---
+### Beispiele der Aktivitätsstufen (max. 4 Punkte)
++1 Punkt: Interaktive Lernaktivitäten  
+→ „Sinnvolle Lernaktivitäten: Interaktiv ist sinnvoll, da man sich hierbei vertieft mit dem Stoff auseinandersetzt, indem man in einer Diskussion Gründe für seine eigene Position äußert.“
++0 Punkte: Konstruktive Lernaktivitäten  
+→ Keine Beispiele wie Mindmaps oder das eigenständige Erstellen von Diagrammen oder Texten genannt.
++0 Punkte: Aktive Lernaktivitäten  
+→ Keine Beispiele wie Unterstreichen oder lautes Vorlesen genannt.
++0 Punkte: Passive Lernaktivitäten  
+→ Keine Beispiele wie das bloße Ansehen von Erklärvideos oder Zuhören genannt.
+Zwischensumme: 1 Punkt  
+---
+### Gesamtpunktzahl: 2 + 0 + 1 = **3 Punkte**</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,99 +217,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -426,133 +544,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="1.8" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
-    <col width="8.1" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="1.85546875" customWidth="1"/>
+    <col min="2" max="3" width="100" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Textaufgabe</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Begruendung</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Punktzahl</t>
-        </is>
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Ausgestaltung:  Cognitive-Load-Theorie  - Grundannahme 1: Arbeitsgedächtnis ist kapazitivbeschränkt  - Grundannahme 2: unterschiedliche Prozesse im Arbeitsgedächtnis während dem Lernen     - inhaltsbedingte kognitive Belastung     - sachfremde kognitive Belastung     - lernrelevante kognitive Belastung  - Grundannahme 3: kognitive Belastungen wirken additiv  - Ziel: sachfremde kognitive Belastung möglichst gering und lernrelevante Belastung möglichst hoch halten  - Vermeidung von Sachen, die nichts mit dem Thema zu tuen haben, also die Vermeidung von sachfremden kognitiven Belastungen (z.B. Hintergrundmusik, komplexe Darstellungen)    Cognitive Theorie of Multimedia Learning (CTML)  - Definition: Annahmen, welche Prozesse im Gedächtnis bei der Verarbeitung von multimedial präsentierten Informationen ablaufen  - Grundannahme 1: Lernen bedeutet aktive Informationsverarbeitung  - Grundannahme 2: Kapazität für Informationsverarbeitung ist massiv beschränkt  - Grundannahme 3: zwei Verarbeitungskanäle sind beteiligt      - visueller-piktorialer Kanal: Verarbeitung von Bildern     - auditorisch-verbaler Kanal: Verarbeitung von Texten  - Besteht aus Bilder und Wörter und gelangt in sensorisches Gedächtnis (Ohren und Augen)  - im Arbeitsgedächtnis: Aufmerksamkeitsprozesse (können nicht alle Informationen verarbeiten)  - Unterscheidung von verbalem und bildhaftem Modell im Arbeitsgedächtnis  - Multimediale Inhalte müssen beide Informationsverarbeitungskanäle ansprechen  - Gründe: effiziente Nutzung der limitierten Verarbeitungskapazität    ICAP-Modell  - Annahmen dazu, in welcher Beziehung äußerlich sichtbare Lernaktivitäten mit unsichtbaren kognitiven Lernprozessen stehen  - Unterscheidung:    - passiv: z.B. ein Erklärvideo ansehen    - aktiv: z.B. in einem Text wichtige Stellen unterstreichen    - konstruktiv: z.B. eine Mindmap erstellen    - interaktiv: z.B. mit Kommilitonen über Lerninhalte diskutieren  - Zentrale Annahme: Wichtigkeit nach folgender Reihenfolge I &gt; C &gt; A &gt; P  - reines Ansehen und Zuhören weniger hilfreich  - Lernenden müssen sich kognitiv intensiv mit Lerninhalten beschäftigen    Studie zur Cognitiv-Load- Theorie  - Studie zum Blutkreisllauf anhand von drei Webseiten  - unterschiedliche Webseiten (Bilder und Text mit Musik, Bilder und Text ohne Musik, Bilder und gesprochener Text mit Musik)  - Wissenserwerb bei visueller Information mit Audioinformation ist am Höchsten  - Reaktionszeiten hat wenig Effekt ohne Audioinformation  - Audiovisuelle präsentierte Informationen werden besser behalten als nur visuell präsentierte Informationen  - Hintergrundmusik erhöht Reaktionszeit  - Lernen ist besser, wenn der Text dazu noch gesprochen wird und Hintergrundmusik sollte aus sein    Studie zu Cognitive Theorie of Multimedia Learning  - Vesuchsaufbau: Materialien wie Blitze entstehen (Videos)  - zwei Versuchsbedingungen    - Text zu Video wurde geschrieben    - Text zu Video wurde gesprochen  - Erinnerungstest nach bestimmter Zeit   - Ergebnis: Teilnehmer, die das Video mit gesprochenem Text gesehen haben, haben besser abgeschnitten  - Animation in Kombination mit eingeblendetem Text überfordert  - Ziel: Lerninhalte sollten sowohl auditive als auch visuelle Kanäle nutzen    Studie zu ICAP-Modell  - Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest  - Zufällige Zuweisung:     - Passiv: Text laut lesen    - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen    - konstruktiv: graphische Darstellung selbstständig vervollständigen    - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen  - Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab   - ICAP- Hypothese wurde bestätigt wie im ICAP-Modell beschrieben  - Lerninhalte sollten nicht einfach nur präsentiert werden, sondern man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)    Prinzipien zur Gestaltung von multimedialen Inhalten  - Multimediaprinzip: Lernerfolg größer, wenn Bilder und Texte enthalten sind  - Modalitätsprinzip: Lerninhalte mit Bildern und Texten ( Lernerfolg besser, wenn Text gesprochen wird)  - Redundanzprinzip: Lerninhalte mit Bildern und Texten sollten nicht wiederholt , sondern ergänzt werden  - Räumliches Kontiguitätsprinzip: Räumlicher Abstand sollte nicht zu groß sein zwischen Bildern/Grafiken und dazugehörigen Texten  - zeitliches Kontiguitätsprinzip: Lerninhalte mit gesprochenem Text und Bildern sollten möglichst gleichzeitig passieren  - Kohärenzprinzip: Multimediale Darstellungen sollten sich auf die Präsentation wesentlicher Informationen beschränken  - Segmentierungsprinzip: bei komplexen Lerninhalten nicht alles auf einmal präsentieren, sondern schrittweise  - Signalisierungsprinzip: durch sprachliche oder visuelle Merker Wichtiges markieren  - Selbsterklärungsprinzip: Lernende verstehen Lerninhalte besser, wenn sie es sich immmer wieder selbst erklären</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>begruendung_lernaktivitaet
-+1 Punkt: Erklärung des ICAP-Modells
-→ „Annahmen dazu, in welcher Beziehung äußerlich sichtbare Lernaktivitäten mit unsichtbaren kognitiven Lernprozessen stehen“
-+1 Punkt: Erklärung der Aktivitätsstufen des Akronyms "ICAP"
-→ „Unterscheidung: - passiv: z.B. ein Erklärvideo ansehen - aktiv: z.B. in einem Text wichtige Stellen unterstreichen - konstruktiv: z.B. eine Mindmap erstellen - interaktiv: z.B. mit Kommilitonen über Lerninhalte diskutieren“
-+1 Punkt: Nennung der Aktivitätsstufe, die verwendet wird
-→ „z.B. mit Kommilitonen über Lerninhalte diskutieren“
-+1 Punkt: Begründung, weshalb diese Aktivitätsstufe gewählt wird
-→ „Wichtigkeit nach folgender Reihenfolge I &gt; C &gt; A &gt; P – reines Ansehen und Zuhören weniger hilfreich – Lernenden müssen sich kognitiv intensiv mit Lerninhalten beschäftigen“
-+2 Punkte: Begründung mittels Studie zu ICAP (Menekse et al., 2013)
-→ „Studie zu ICAP-Modell - Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest – Zufällige Zuweisung: - Passiv: Text laut lesen - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen - konstruktiv: graphische Darstellung selbstständig vervollständigen - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen - Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab - ICAP- Hypothese wurde bestätigt wie im ICAP-Modell beschrieben – Lerninhalte sollten nicht einfach nur präsentiert werden, sondern man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)“
-+1 Punkt: Nennung der Teilnehmeranzahl (TN): 120 TNs
-→ „120 TNs“
-+1 Punkt: Versuchsaufbau/ Versuchsbedingungen: Vier Gruppen zum Thema Chemie mit vier Bedingungen
-→ „Ablauf im Bereich Chemie: Vorwissenstest, zweiseitiger Einführungstest zum Lesen, achtseitiger Informationstext, Nachwissenstest – Zufällige Zuweisung: - Passiv: Text laut lesen - aktiv: Text laut lesen und wichtigste Inhalte unterstreichen - konstruktiv: graphische Darstellung selbstständig vervollständigen - interaktiv: graphische Darstellung in Zweiergruppen vervollständigen“
-+1 Punkt: Ergebnisse: Bestätigung der ICAP-Hypothese, dass Interaktive Lernaktivitäten das höchste Potenzial haben, gefolgt von konstruktiven, gefolgt von aktiven und gefolgt von passiven
-→ „Ergebnis: Vortest relativ gleich, im Nachtest schneidet interaktiv am Besten ab - ICAP- Hypothese wurde bestätigt wie im ICAP-Modell beschrieben“
-+1 Punkt: 1. Implikation: Lerninhalte sollten nicht einfach nur präsentiert werden
-→ „Lerninhalte sollten nicht einfach nur präsentiert werden“
-+1 Punkt: 2. Implikation: Lehrperson sollte Gelegenheiten für interaktive Aktivitäten schaffen
-→ „man sollte Gelegenheiten für interaktive Aktivitäten Schaffen (Gruppenarbeiten)“
-+1 Punkt: Interaktive Lernaktivitäten: Vervollständigung einer graphischen Darstellung in Zweiergruppen/ mit anderen diskutieren
-→ „graphische Darstellung in Zweiergruppen vervollständigen“
-+1 Punkt: konstruktive Lernaktivitäten: Graphische Darstellung selbstständig und allein vervollständigen/ eine Mindmap erstellen
-→ „graphische Darstellung selbstständig vervollständigen“
-+1 Punkt: aktive Lernaktivitäten: Informationstext laut vorlesen und wichtigste Inhalte unterstreichen/
-→ „Text laut lesen und wichtigste Inhalte unterstreichen“
-+1 Punkt: passive Lernaktivitäten: Informationstext laut vorlesen/ Erklärvideo ansehen
-→ „Text laut lesen“
-Gesamtpunktzahl: 15</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
+    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>AG0EVJU2003FU  Notizen:     cognitive-load-theorie   = wie wir Lernmaterialien nutzen  wie Informationen aus dem Arbeitsgedächtnis verarbeitet werden, dies ist begrenzt  ungünstig: Hintergrundmusik, die nichts mit dem Lernenden zu tun hat  günstig: was man aufwendet, um neue Schemata zu lernen  Personen mit hoher inhaltsbedingte Belastung - ebenso hohe sachfremde B. - ist lernen kaum möglich   Personen mit niedriger inhaltsbedingte Belastung aufgrund von Vorwissen - ebenso niedrige sachfremde B. - Potenzial zum lernen lernen möglich   man soll darauf achten, dass sachfremde Belastung gering ist und keine Ablenkung von Hintergrundmusik      Eine exemplarische empirische Studie zur Cognitive-Load-Theory  2004 10 Hochschulstudenten erhielten Informationssystem zum Thema   Blutkreislauf   3 Webseiten:  1. visuelle Bilder + Text + ohne Hintergrundmusik  2. visuelle Bilder + Text + Hintergrundmusik  3. visuelle Bilder + Text vorgelesen + Hintergrundmusik    Wie lernen sie/ was nehmen sie mit? Wie ist Reaktionszeit auf Ton?   man lernt anscheinend mehr, wenn Bilder mit Ton vorhanden ist   bei nur visueller Informationen Hintergrundmusik relativ egal, bei zusätzlichen audio Informativen eher keine Hintergrundmusik    Das ICAP-Modell von Chi &amp; Wylie  passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen   körperlich aktive = wichtige Infos unterstreichen   konstruktiv = Mindmap erstellen  interaktiv = mit anderen austauschen -  am besten - neues wissen produzieren - tiefes Verständnis   also reines zuhören nicht so gut !  aber nur wenn Auseinandersetzung auch über das Lernende ist    Eine exemplarische empirische Studie zum ICAP-Modell  120 Studierende  zum Thema Chemie   Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest   interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten  daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !     Die Cognitive Theory of Multimedia Learning (CTML) von Mayer  welche Prozesse laufen ab, wenn wir Multimedia benutzen   Multimedia = bild + wörter meistens -&gt; sensorisches Gedächtnis -&gt; Arbeitsgedächtnis: alle Infos können wir nicht gleichzeitig aufnehmen  dann Integration mit Vorwissen -&gt; dann lernen     daher beide Kanäle ansprechen !  Überlastung eines der beiden Kanäle sollte vermieden werden!    Eine exemplarische empirische Studie zur Cognitive Theory of Multimedia Learning (CTML)  1: Bilder + geschriebener Text  2. Bilder + vorgelesener Text  danach Erinnerungstest   bildlicher Inhalt muss mit auditiven Inhalt passend sein! multimediales lernen ist besser!    Evidenzbasierte Prinzipien zur Gestaltung von multimedialen Inhalten  Powerpointfolien im Vortrag - grafische Darstellung  Videos mit Text  Infos räumlich nah und relativ nah im zeitlichen abstand   Comic in einer ecke nicht gut, da so Aufmerksamkeit abgelenkt wird    Aufgabenstellung:     Mit den jetzigen Informationen würde ich meine Präsentation mit einer PowerPoint untermalen, auf welcher überwiegend Bilder zu sehen sind, welche ich gleichzeitig mit Worten erkläre. So wird die audio und visuelle Belastung angesprochen. Daher weniger Text, da man sich vorgelesenen Text besser merken kann (siehe Cognitive Theory of Multimedia). Zusätzlich würde ich anfangs auf Themen aus dem Unterricht oder ganz allgemeine Themen ansprechen, so dass jeder bei dem gleichen Wissenstand abgeholt werden kann bei gleicher inhaltsbedingter Belastung (siehe Cognitive-Load-Theory). Außerdem würde ich auch ein Video zeigen, welches das Gezeigte und Gesprochene noch einmal mit Hintergrundmusik wiederholt. Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.   daher würde ich alle Lernaktivitäten miteinander vereinen, um den bestmöglichen Vortrag zu haben.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>## Kategorie
-begruendung_lernaktivitaet
-+1 Punkt: Erklärung des ICAP-Modells
-→ „Das ICAP-Modell von Chi &amp; Wylie passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen körperlich aktive = wichtige Infos unterstreichen konstruktiv = Mindmap erstellen interaktiv = mit anderen austauschen - am besten - neues wissen produzieren - tiefes Verständnis also reines zuhören nicht so gut ! aber nur wenn Auseinandersetzung auch über das Lernende ist“
-+1 Punkt: Erklärung der Aktivitätsstufen des Akronyms „ICAP“
-→ „passive Aktivitäten = Erklärvideo oder Vortrag anhören - am schlechtesten - neues wissen entsteht, aber nicht verknüpft mit aktuellem wissen körperlich aktive = wichtige Infos unterstreichen konstruktiv = Mindmap erstellen interaktiv = mit anderen austauschen - am besten - neues wissen produzieren - tiefes Verständnis“
-+1 Punkt: Nennung der Aktivitätsstufe, die verwendet wird
-→ „Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.“
-+1 Punkt: Begründung, weshalb diese Aktivitätsstufe gewählt wird
-→ „daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !“
-+2 Punkte: Begründung mittels Studie zu ICAP (Menekse et al., 2013)
-→ „Eine exemplarische empirische Studie zum ICAP-Modell 120 Studierende zum Thema Chemie Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten“
-+1 Punkt: Nennung der Teilnehmeranzahl (TN): 120 TNs
-→ „Eine exemplarische empirische Studie zum ICAP-Modell 120 Studierende zum Thema Chemie“
-+1 Punkt: Versuchsaufbau/Versuchsbedingungen: Vier Gruppen zum Thema Chemie mit vier Bedingungen
-→ „Vorwissentest - 8 Seiten Infotext (unterschiedliche Herangehensweise) - Nachtest“
-+1 Punkt: Ergebnisse: Bestätigung der ICAP-Hypothese, dass Interaktive Lernaktivitäten das höchste Potenzial haben, gefolgt von konstruktiven, gefolgt von aktiven und gefolgt von passiven
-→ „interaktive Aktivitäten am Besten im Nachtest, passiv am Schlechtesten“
-+1 Punkt: 1. Implikation: Lerninhalte sollten nicht einfach nur präsentiert werden
-→ „daher nicht nur präsentieren, sondern auch interaktive Aktivitäten (Kleingruppen) !“ 
-+1 Punkt: 2. Implikation: Lehrperson sollte Gelegenheiten für interaktive Aktivitäten schaffen
-→ „Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.“
-+1 Punkt: Interaktive Lernaktivitäten: Vervollständigung einer graphischen Darstellung in Zweiergruppen/mit anderen diskutieren
-→  Zuletzt würde ich nach dem IPAC- Modell noch eine Diskussion starten, so dass die bis dahin nur Zuhörenden interaktiv sich austauschen und ihre Gedankengänge dazu sagen können.
-Gesamtpunktzahl: 12</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
